--- a/data/trans_camb/IP1005-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1005-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>0,0; 4,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,0</t>
+          <t>-3,25; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,18</t>
+          <t>-1,89; 1,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,0</t>
+          <t>-1,69; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,55</t>
+          <t>-0,61; 1,57</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>0,0; 4,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,77</t>
+          <t>0,0; 4,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,29</t>
+          <t>0,0; 7,02</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,76</t>
+          <t>0,0; 6,57</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 3,81</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 0,0</t>
+          <t>-2,63; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,0</t>
+          <t>-3,32; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,93</t>
+          <t>-1,54; 0,94</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 0,0</t>
+          <t>-2,57; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,45</t>
+          <t>-1,3; 0,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,0</t>
+          <t>-1,78; 0,0</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,19</t>
+          <t>-1,23; 0,81</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,59</t>
+          <t>-1,64; 0,58</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,79</t>
+          <t>-2,08; 0,79</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,78</t>
+          <t>-1,36; 1,79</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,61</t>
+          <t>-1,07; 0,59</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,97</t>
+          <t>-0,88; 0,94</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-97,62; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,39</t>
+          <t>-0,51; 0,38</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,5</t>
+          <t>-0,41; 0,51</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,27</t>
+          <t>-0,47; 0,28</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,88</t>
+          <t>-0,22; 0,83</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,23</t>
+          <t>-0,39; 0,18</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,51</t>
+          <t>-0,19; 0,49</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-89,34; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1970,17 +1970,17 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-68,2; —</t>
+          <t>-73,1; —</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-83,3; 236,25</t>
+          <t>-83,34; 171,45</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-48,43; 407,83</t>
+          <t>-47,05; 370,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1005-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1005-Provincia-trans_camb.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,09</t>
+          <t>0,0; 4,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,0</t>
+          <t>-3,16; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,18</t>
+          <t>-1,94; 1,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 3,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,0</t>
+          <t>-1,21; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,57</t>
+          <t>-0,6; 1,52</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>0,0; 4,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,02</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 3,03</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,02</t>
+          <t>0,0; 7,1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,57</t>
+          <t>0,0; 6,6</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,81</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,0</t>
+          <t>-2,98; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,94</t>
+          <t>-1,88; 0,93</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,0</t>
+          <t>-2,37; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,0</t>
+          <t>-2,04; 0,0</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,81</t>
+          <t>-1,24; 0,81</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,58</t>
+          <t>-1,24; 0,59</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,79</t>
+          <t>-1,98; 0,79</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,79</t>
+          <t>-1,26; 2,01</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,59</t>
+          <t>-1,22; 0,68</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,94</t>
+          <t>-0,85; 0,95</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,38</t>
+          <t>-0,5; 0,37</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,51</t>
+          <t>-0,41; 0,55</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,28</t>
+          <t>-0,48; 0,27</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,83</t>
+          <t>-0,22; 0,82</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,18</t>
+          <t>-0,38; 0,22</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,49</t>
+          <t>-0,22; 0,48</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1970,17 +1970,17 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-73,1; —</t>
+          <t>-73,89; 1195,53</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-83,34; 171,45</t>
+          <t>-83,73; 231,72</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 370,12</t>
+          <t>-56,44; 340,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1005-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1005-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -598,17 +598,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,83</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
     </row>
@@ -674,17 +674,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,65</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,62</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,04</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,17</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,14; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>-1,91; 1,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,0</t>
+          <t>-1,5; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,52</t>
+          <t>-0,6; 1,55</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-6,66%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,79</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,57</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,99</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,85</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,75</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,03</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1,28</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>1,24</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,76</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 3,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-0,52</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-0,52</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,0</t>
+          <t>-1,53; 0,93</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 0,0</t>
+          <t>-2,76; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,93</t>
+          <t>-2,9; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,0</t>
+          <t>-3,22; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,45</t>
+          <t>-1,31; 0,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,0</t>
+          <t>-1,54; 0,0</t>
         </is>
       </c>
     </row>
@@ -1605,17 +1605,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-7,91%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-7,91%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-0,01</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-0,11</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>0,24</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,81</t>
+          <t>-2,06; 0,79</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,59</t>
+          <t>-1,57; 1,78</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,79</t>
+          <t>-1,24; 1,19</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,01</t>
+          <t>-1,3; 0,59</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,68</t>
+          <t>-1,2; 0,61</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,95</t>
+          <t>-0,89; 0,97</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-50,09%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>30,77%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-1,3%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>-28,24%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-50,09%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>30,77%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-97,62; —</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>0,25</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>-0,03</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>0,04</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>0,25</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,37</t>
+          <t>-0,56; 0,27</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,55</t>
+          <t>-0,22; 0,88</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,27</t>
+          <t>-0,48; 0,39</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,82</t>
+          <t>-0,42; 0,5</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,22</t>
+          <t>-0,35; 0,23</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,48</t>
+          <t>-0,19; 0,51</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-34,16%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>89,61%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>-11,12%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>15,1%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-34,16%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>89,61%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-68,2; —</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1970,17 +1970,17 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-73,89; 1195,53</t>
+          <t>-89,34; —</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-83,73; 231,72</t>
+          <t>-83,3; 236,25</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-56,44; 340,48</t>
+          <t>-48,43; 407,83</t>
         </is>
       </c>
     </row>
